--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3254C9C7-FC4E-3648-B1E4-D7D4ADA30432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E044DA3-987D-A940-B204-DC3CC0BDA10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22040" yWindow="-15060" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="22040" yWindow="-14700" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Fork</t>
   </si>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>WhiskyMCX</t>
+  </si>
+  <si>
+    <t>Fox 32 TC</t>
+  </si>
+  <si>
+    <t>40,50</t>
+  </si>
+  <si>
+    <t>45,50</t>
   </si>
 </sst>
 </file>
@@ -109,10 +118,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,12 +457,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="10.83203125" style="1"/>
+    <col min="3" max="3" width="11.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -586,6 +597,20 @@
         <v>50</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E044DA3-987D-A940-B204-DC3CC0BDA10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB5EA72-0285-C44F-8BD3-86B421E1684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22040" yWindow="-14700" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="39600" yWindow="-18120" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Fork</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>45,50</t>
+  </si>
+  <si>
+    <t>Taïga Fork</t>
   </si>
 </sst>
 </file>
@@ -457,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -611,6 +614,20 @@
         <v>13</v>
       </c>
     </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>500</v>
+      </c>
+      <c r="D9" s="1">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB5EA72-0285-C44F-8BD3-86B421E1684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFCF518-1F30-4D4C-A025-C421C7CFFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39600" yWindow="-18120" windowWidth="27640" windowHeight="16440" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="7260" yWindow="1180" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Fork</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Taïga Fork</t>
+  </si>
+  <si>
+    <t>Fox 34 SC 130 mm</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -546,30 +549,27 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C4" s="1">
-        <v>395</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
       </c>
       <c r="C5" s="1">
-        <v>398</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46</v>
+        <v>395</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -580,51 +580,65 @@
         <v>0</v>
       </c>
       <c r="C6" s="1">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D6" s="1">
-        <v>55.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D7" s="1">
-        <v>50</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0</v>
+      </c>
+      <c r="C8" s="1">
+        <v>415</v>
+      </c>
+      <c r="D8" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>0</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="1">
         <v>500</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D10" s="1">
         <v>51</v>
       </c>
     </row>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFCF518-1F30-4D4C-A025-C421C7CFFE0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32956391-101C-6A40-BA96-67C626D68540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7260" yWindow="1180" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32956391-101C-6A40-BA96-67C626D68540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B731007-04E3-3F4E-97D1-725A6EC17492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="2700" yWindow="2940" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Fork</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Fox 34 SC 130 mm</t>
+  </si>
+  <si>
+    <t>Enve Gravel In-Route</t>
+  </si>
+  <si>
+    <t>53, 55</t>
   </si>
 </sst>
 </file>
@@ -463,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -560,30 +566,27 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C5" s="1">
         <v>395</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" s="1">
         <v>0</v>
       </c>
       <c r="C6" s="1">
-        <v>398</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46</v>
+        <v>395</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -594,51 +597,65 @@
         <v>0</v>
       </c>
       <c r="C7" s="1">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D7" s="1">
-        <v>55.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="1">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D8" s="1">
-        <v>50</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1">
+        <v>415</v>
+      </c>
+      <c r="D9" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="1">
         <v>0</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C11" s="1">
         <v>500</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D11" s="1">
         <v>51</v>
       </c>
     </row>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B731007-04E3-3F4E-97D1-725A6EC17492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702CCA3-06C2-AF4C-A2C2-2F118D7C8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="2940" windowWidth="28800" windowHeight="17500" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="17120" windowHeight="14060" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -469,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -478,7 +478,7 @@
     <col min="4" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,16 +492,19 @@
         <v>2</v>
       </c>
       <c r="E1" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.2</v>
       </c>
-      <c r="F1" s="2">
+      <c r="G1" s="2">
         <v>0.25</v>
       </c>
-      <c r="G1" s="2">
+      <c r="H1" s="2">
         <v>0.3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -516,18 +519,22 @@
       </c>
       <c r="E2" s="1">
         <f>$C2-E1*100</f>
+        <v>488.7</v>
+      </c>
+      <c r="F2" s="1">
+        <f>$C2-F1*100</f>
         <v>483.7</v>
       </c>
-      <c r="F2" s="1">
-        <f t="shared" ref="F2:G2" si="0">$C2-F1*100</f>
+      <c r="G2" s="1">
+        <f>$C2-G1*100</f>
         <v>478.7</v>
       </c>
-      <c r="G2" s="1">
-        <f t="shared" si="0"/>
+      <c r="H2" s="1">
+        <f>$C2-H1*100</f>
         <v>473.7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -542,18 +549,22 @@
       </c>
       <c r="E3" s="1">
         <f>$C3 - E1*120</f>
+        <v>512</v>
+      </c>
+      <c r="F3" s="1">
+        <f>$C3 - F1*120</f>
         <v>506</v>
       </c>
-      <c r="F3" s="1">
-        <f t="shared" ref="F3:G3" si="1">$C3 - F1*120</f>
+      <c r="G3" s="1">
+        <f>$C3 - G1*120</f>
         <v>500</v>
       </c>
-      <c r="G3" s="1">
-        <f t="shared" si="1"/>
+      <c r="H3" s="1">
+        <f>$C3 - H1*120</f>
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -564,7 +575,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -575,7 +586,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -589,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -603,7 +614,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -617,7 +628,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -631,7 +642,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -645,7 +656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4702CCA3-06C2-AF4C-A2C2-2F118D7C8818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11F7ED7-8157-F147-B0C9-E582CF51B63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="17120" windowHeight="14060" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>Fork</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>53, 55</t>
+  </si>
+  <si>
+    <t>Rockshox Sid</t>
   </si>
 </sst>
 </file>
@@ -469,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -575,98 +578,134 @@
         <v>540</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>100</v>
       </c>
       <c r="C5" s="1">
-        <v>395</v>
+        <v>506</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1">
-        <v>395</v>
+        <v>531</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
-        <v>398</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46</v>
+        <v>395</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
       <c r="C8" s="1">
-        <v>406</v>
-      </c>
-      <c r="D8" s="1">
-        <v>55.5</v>
+        <v>395</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1">
         <v>0</v>
       </c>
       <c r="C9" s="1">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="D9" s="1">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>406</v>
+      </c>
+      <c r="D10" s="1">
+        <v>55.5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
       <c r="C11" s="1">
+        <v>415</v>
+      </c>
+      <c r="D11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1">
         <v>500</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D13" s="1">
         <v>51</v>
       </c>
     </row>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11F7ED7-8157-F147-B0C9-E582CF51B63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFD53A0-4E95-0D44-B486-B809ACED339D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
+    <workbookView xWindow="2040" yWindow="3520" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
   <si>
     <t>Fork</t>
   </si>
@@ -93,13 +93,28 @@
   </si>
   <si>
     <t>Rockshox Sid</t>
+  </si>
+  <si>
+    <t>DT Swiss F232 One 100 mm</t>
+  </si>
+  <si>
+    <t>DT Swiss F232 One 110 mm</t>
+  </si>
+  <si>
+    <t>DT Swiss F232 One 120 mm</t>
+  </si>
+  <si>
+    <t>Rockshox Pike</t>
+  </si>
+  <si>
+    <t>Rockshox Recon Silver RL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -111,6 +126,12 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -472,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -521,19 +542,19 @@
         <v>4</v>
       </c>
       <c r="E2" s="1">
-        <f>$C2-E1*100</f>
+        <f>$C2-E$1*$B2</f>
         <v>488.7</v>
       </c>
       <c r="F2" s="1">
-        <f>$C2-F1*100</f>
+        <f t="shared" ref="F2:H12" si="0">$C2-F$1*$B2</f>
         <v>483.7</v>
       </c>
       <c r="G2" s="1">
-        <f>$C2-G1*100</f>
+        <f t="shared" si="0"/>
         <v>478.7</v>
       </c>
       <c r="H2" s="1">
-        <f>$C2-H1*100</f>
+        <f t="shared" si="0"/>
         <v>473.7</v>
       </c>
     </row>
@@ -551,19 +572,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="1">
-        <f>$C3 - E1*120</f>
+        <f t="shared" ref="E3:E12" si="1">$C3-E$1*$B3</f>
         <v>512</v>
       </c>
       <c r="F3" s="1">
-        <f>$C3 - F1*120</f>
+        <f t="shared" si="0"/>
         <v>506</v>
       </c>
       <c r="G3" s="1">
-        <f>$C3 - G1*120</f>
+        <f t="shared" si="0"/>
         <v>500</v>
       </c>
       <c r="H3" s="1">
-        <f>$C3 - H1*120</f>
+        <f t="shared" si="0"/>
         <v>494</v>
       </c>
     </row>
@@ -577,6 +598,22 @@
       <c r="C4" s="1">
         <v>540</v>
       </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>520.5</v>
+      </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>514</v>
+      </c>
+      <c r="G4" s="1">
+        <f t="shared" si="0"/>
+        <v>507.5</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>501</v>
+      </c>
     </row>
     <row r="5" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -591,10 +628,22 @@
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="E5" s="1">
+        <f t="shared" si="1"/>
+        <v>491</v>
+      </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>486</v>
+      </c>
+      <c r="G5" s="1">
+        <f t="shared" si="0"/>
+        <v>481</v>
+      </c>
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>476</v>
+      </c>
     </row>
     <row r="6" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -609,107 +658,298 @@
       <c r="D6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>513</v>
+      </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>507</v>
+      </c>
+      <c r="G6" s="1">
+        <f t="shared" si="0"/>
+        <v>501</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="B7" s="1">
+        <v>100</v>
       </c>
       <c r="C7" s="1">
-        <v>395</v>
+        <v>507</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="1"/>
+        <v>492</v>
+      </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>487</v>
+      </c>
+      <c r="G7" s="1">
+        <f t="shared" si="0"/>
+        <v>482</v>
+      </c>
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B8" s="1">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="C8" s="1">
-        <v>395</v>
+        <v>517</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>500.5</v>
+      </c>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+      <c r="G8" s="1">
+        <f t="shared" si="0"/>
+        <v>489.5</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>484</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B9" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C9" s="1">
-        <v>398</v>
-      </c>
-      <c r="D9" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="1"/>
+        <v>509</v>
+      </c>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>503</v>
+      </c>
+      <c r="G9" s="1">
+        <f t="shared" si="0"/>
+        <v>497</v>
+      </c>
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C10" s="1">
-        <v>406</v>
+        <v>531</v>
       </c>
       <c r="D10" s="1">
-        <v>55.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>513</v>
+      </c>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>507</v>
+      </c>
+      <c r="G10" s="1">
+        <f t="shared" si="0"/>
+        <v>501</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1">
-        <v>0</v>
-      </c>
-      <c r="C11" s="1">
-        <v>415</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
+        <v>-19.5</v>
+      </c>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>-26</v>
+      </c>
+      <c r="G11" s="1">
+        <f t="shared" si="0"/>
+        <v>-32.5</v>
+      </c>
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="B12" s="1">
+        <v>120</v>
+      </c>
+      <c r="C12" s="1">
+        <v>533</v>
+      </c>
+      <c r="D12" s="1">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>515</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>509</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>503</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>497</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>395</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>395</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>398</v>
+      </c>
+      <c r="D15" s="1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>406</v>
+      </c>
+      <c r="D16" s="1">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>415</v>
+      </c>
+      <c r="D17" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B19" s="1">
         <v>0</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C19" s="1">
         <v>500</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D19" s="1">
         <v>51</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFD53A0-4E95-0D44-B486-B809ACED339D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB465FCD-EDF7-214E-AA08-E725D55FF373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2040" yWindow="3520" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
   <si>
     <t>Fork</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Rockshox Recon Silver RL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rockshox </t>
+  </si>
+  <si>
+    <t>Fox</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -948,6 +954,43 @@
         <v>51</v>
       </c>
     </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="1">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB465FCD-EDF7-214E-AA08-E725D55FF373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125214CC-6957-1540-9F60-BC12BC634265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2040" yWindow="3520" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>Fork</t>
   </si>
@@ -552,7 +552,7 @@
         <v>488.7</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:H12" si="0">$C2-F$1*$B2</f>
+        <f t="shared" ref="F2:H13" si="0">$C2-F$1*$B2</f>
         <v>483.7</v>
       </c>
       <c r="G2" s="1">
@@ -578,7 +578,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E12" si="1">$C3-E$1*$B3</f>
+        <f t="shared" ref="E3:E13" si="1">$C3-E$1*$B3</f>
         <v>512</v>
       </c>
       <c r="F3" s="1">
@@ -635,19 +635,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <f t="shared" si="1"/>
+        <f>$C5-E$1*$B5</f>
         <v>491</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="0"/>
+        <f>$C5-F$1*$B5</f>
         <v>486</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="0"/>
+        <f>$C5-G$1*$B5</f>
         <v>481</v>
       </c>
       <c r="H5" s="1">
-        <f t="shared" si="0"/>
+        <f>$C5-H$1*$B5</f>
         <v>476</v>
       </c>
     </row>
@@ -656,149 +656,147 @@
         <v>18</v>
       </c>
       <c r="B6" s="1">
+        <v>110</v>
+      </c>
+      <c r="C6" s="1">
+        <v>516</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1">
+        <f>$C6-E$1*$B6</f>
+        <v>499.5</v>
+      </c>
+      <c r="F6" s="1">
+        <f>$C6-F$1*$B6</f>
+        <v>494</v>
+      </c>
+      <c r="G6" s="1">
+        <f>$C6-G$1*$B6</f>
+        <v>488.5</v>
+      </c>
+      <c r="H6" s="1">
+        <f>$C6-H$1*$B6</f>
+        <v>483</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1">
         <v>120</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C7" s="1">
         <v>531</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E7" s="1">
         <f t="shared" si="1"/>
         <v>513</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>507</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G7" s="1">
         <f t="shared" si="0"/>
         <v>501</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H7" s="1">
         <f t="shared" si="0"/>
         <v>495</v>
       </c>
     </row>
-    <row r="7" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="8" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="1">
         <v>100</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C8" s="1">
         <v>507</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E8" s="1">
         <f t="shared" si="1"/>
         <v>492</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>487</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G8" s="1">
         <f t="shared" si="0"/>
         <v>482</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H8" s="1">
         <f t="shared" si="0"/>
         <v>477</v>
       </c>
     </row>
-    <row r="8" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="9" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="1">
         <v>110</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C9" s="1">
         <v>517</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E9" s="1">
         <f t="shared" si="1"/>
         <v>500.5</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F9" s="1">
         <f t="shared" si="0"/>
         <v>495</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G9" s="1">
         <f t="shared" si="0"/>
         <v>489.5</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H9" s="1">
         <f t="shared" si="0"/>
         <v>484</v>
       </c>
     </row>
-    <row r="9" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>120</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C10" s="1">
         <v>527</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E10" s="1">
         <f t="shared" si="1"/>
         <v>509</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>503</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G10" s="1">
         <f t="shared" si="0"/>
         <v>497</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H10" s="1">
         <f t="shared" si="0"/>
         <v>491</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1">
-        <v>120</v>
-      </c>
-      <c r="C10" s="1">
-        <v>531</v>
-      </c>
-      <c r="D10" s="1">
-        <v>44</v>
-      </c>
-      <c r="E10" s="1">
-        <f t="shared" si="1"/>
-        <v>513</v>
-      </c>
-      <c r="F10" s="1">
-        <f t="shared" si="0"/>
-        <v>507</v>
-      </c>
-      <c r="G10" s="1">
-        <f t="shared" si="0"/>
-        <v>501</v>
-      </c>
-      <c r="H10" s="1">
-        <f t="shared" si="0"/>
-        <v>495</v>
       </c>
     </row>
     <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
@@ -806,96 +804,112 @@
         <v>22</v>
       </c>
       <c r="B11" s="1">
-        <v>130</v>
-      </c>
-      <c r="C11" s="1"/>
+        <v>120</v>
+      </c>
+      <c r="C11" s="1">
+        <v>531</v>
+      </c>
       <c r="D11" s="1">
         <v>44</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>-19.5</v>
+        <v>513</v>
       </c>
       <c r="F11" s="1">
         <f t="shared" si="0"/>
-        <v>-26</v>
+        <v>507</v>
       </c>
       <c r="G11" s="1">
         <f t="shared" si="0"/>
-        <v>-32.5</v>
+        <v>501</v>
       </c>
       <c r="H11" s="1">
         <f t="shared" si="0"/>
-        <v>-39</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="1">
-        <v>120</v>
-      </c>
-      <c r="C12" s="1">
-        <v>533</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
+        <v>-19.5</v>
+      </c>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>-26</v>
+      </c>
+      <c r="G12" s="1">
+        <f t="shared" si="0"/>
+        <v>-32.5</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1">
+        <v>120</v>
+      </c>
+      <c r="C13" s="1">
+        <v>533</v>
+      </c>
+      <c r="D13" s="1">
+        <v>42</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="1"/>
         <v>515</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F13" s="1">
         <f t="shared" si="0"/>
         <v>509</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G13" s="1">
         <f t="shared" si="0"/>
         <v>503</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H13" s="1">
         <f t="shared" si="0"/>
         <v>497</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="1">
-        <v>395</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C14" s="1">
         <v>395</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
       <c r="C15" s="1">
-        <v>398</v>
-      </c>
-      <c r="D15" s="1">
-        <v>46</v>
+        <v>395</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -906,60 +920,66 @@
         <v>0</v>
       </c>
       <c r="C16" s="1">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D16" s="1">
-        <v>55.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1">
         <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D17" s="1">
-        <v>50</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>415</v>
+      </c>
+      <c r="D18" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B20" s="1">
         <v>0</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20" s="1">
         <v>500</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -967,7 +987,10 @@
         <v>24</v>
       </c>
       <c r="B22" s="1">
-        <v>40</v>
+        <v>30</v>
+      </c>
+      <c r="C22" s="1">
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -975,7 +998,10 @@
         <v>24</v>
       </c>
       <c r="B23" s="1">
-        <v>50</v>
+        <v>40</v>
+      </c>
+      <c r="C23" s="1">
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -983,12 +1009,15 @@
         <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="B25" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125214CC-6957-1540-9F60-BC12BC634265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B377E050-D7DD-864A-9712-38ED33C43525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2040" yWindow="3520" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
   <si>
     <t>Fork</t>
   </si>
@@ -110,10 +110,13 @@
     <t>Rockshox Recon Silver RL</t>
   </si>
   <si>
-    <t xml:space="preserve">Rockshox </t>
-  </si>
-  <si>
-    <t>Fox</t>
+    <t>Rockshox Rudy XL</t>
+  </si>
+  <si>
+    <t>Rockshox Rudy/Fox TC</t>
+  </si>
+  <si>
+    <t>Rockshox Fox TC</t>
   </si>
 </sst>
 </file>
@@ -984,7 +987,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22" s="1">
         <v>30</v>
@@ -995,7 +998,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1">
         <v>40</v>
@@ -1006,18 +1009,24 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1">
         <v>50</v>
       </c>
+      <c r="C24" s="1">
+        <v>445</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1">
         <v>60</v>
+      </c>
+      <c r="C25" s="1">
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/data/helper/Fork data.xlsx
+++ b/data/helper/Fork data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/helper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B377E050-D7DD-864A-9712-38ED33C43525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1476BB55-950E-B24D-A51D-3B9E25DCC8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2040" yWindow="3520" windowWidth="25780" windowHeight="13840" xr2:uid="{7C5FB5DD-0678-0A44-B500-626A7C5158D9}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>Fork</t>
   </si>
@@ -502,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{575F23C2-FDDA-F54D-85AF-8D9D6DE0AEFD}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" style="1" bestFit="1" customWidth="1"/>
@@ -555,7 +555,7 @@
         <v>488.7</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:H13" si="0">$C2-F$1*$B2</f>
+        <f t="shared" ref="F2:H14" si="0">$C2-F$1*$B2</f>
         <v>483.7</v>
       </c>
       <c r="G2" s="1">
@@ -581,7 +581,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E13" si="1">$C3-E$1*$B3</f>
+        <f t="shared" ref="E3:E14" si="1">$C3-E$1*$B3</f>
         <v>512</v>
       </c>
       <c r="F3" s="1">
@@ -638,19 +638,19 @@
         <v>4</v>
       </c>
       <c r="E5" s="1">
-        <f>$C5-E$1*$B5</f>
+        <f t="shared" ref="E5:H6" si="2">$C5-E$1*$B5</f>
         <v>491</v>
       </c>
       <c r="F5" s="1">
-        <f>$C5-F$1*$B5</f>
+        <f t="shared" si="2"/>
         <v>486</v>
       </c>
       <c r="G5" s="1">
-        <f>$C5-G$1*$B5</f>
+        <f t="shared" si="2"/>
         <v>481</v>
       </c>
       <c r="H5" s="1">
-        <f>$C5-H$1*$B5</f>
+        <f t="shared" si="2"/>
         <v>476</v>
       </c>
     </row>
@@ -666,19 +666,19 @@
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1">
-        <f>$C6-E$1*$B6</f>
+        <f t="shared" si="2"/>
         <v>499.5</v>
       </c>
       <c r="F6" s="1">
-        <f>$C6-F$1*$B6</f>
+        <f t="shared" si="2"/>
         <v>494</v>
       </c>
       <c r="G6" s="1">
-        <f>$C6-G$1*$B6</f>
+        <f t="shared" si="2"/>
         <v>488.5</v>
       </c>
       <c r="H6" s="1">
-        <f>$C6-H$1*$B6</f>
+        <f t="shared" si="2"/>
         <v>483</v>
       </c>
     </row>
@@ -839,94 +839,112 @@
       <c r="B12" s="1">
         <v>130</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>541</v>
+      </c>
       <c r="D12" s="1">
         <v>44</v>
       </c>
       <c r="E12" s="1">
         <f t="shared" si="1"/>
-        <v>-19.5</v>
+        <v>521.5</v>
       </c>
       <c r="F12" s="1">
         <f t="shared" si="0"/>
-        <v>-26</v>
+        <v>515</v>
       </c>
       <c r="G12" s="1">
         <f t="shared" si="0"/>
-        <v>-32.5</v>
+        <v>508.5</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="0"/>
-        <v>-39</v>
+        <v>502</v>
       </c>
     </row>
     <row r="13" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="C13" s="1">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="D13" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="1"/>
+        <v>530</v>
+      </c>
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>523</v>
+      </c>
+      <c r="G13" s="1">
+        <f t="shared" si="0"/>
+        <v>516</v>
+      </c>
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>509</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1">
+        <v>120</v>
+      </c>
+      <c r="C14" s="1">
+        <v>533</v>
+      </c>
+      <c r="D14" s="1">
+        <v>42</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
         <v>515</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F14" s="1">
         <f t="shared" si="0"/>
         <v>509</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G14" s="1">
         <f t="shared" si="0"/>
         <v>503</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H14" s="1">
         <f t="shared" si="0"/>
         <v>497</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="1">
-        <v>395</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
         <v>395</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1">
         <v>0</v>
       </c>
       <c r="C16" s="1">
-        <v>398</v>
-      </c>
-      <c r="D16" s="1">
-        <v>46</v>
+        <v>395</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -937,63 +955,66 @@
         <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="D17" s="1">
-        <v>55.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1">
         <v>0</v>
       </c>
       <c r="C18" s="1">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="D18" s="1">
-        <v>50</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="3">
-        <v>435445</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>415</v>
+      </c>
+      <c r="D19" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="3">
+        <v>435445</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B21" s="1">
         <v>0</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C21" s="1">
         <v>500</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1">
-        <v>30</v>
-      </c>
-      <c r="C22" s="1">
-        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1001,31 +1022,42 @@
         <v>25</v>
       </c>
       <c r="B23" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1">
-        <v>435</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1">
-        <v>445</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="1">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B26" s="1">
         <v>60</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C26" s="1">
         <v>470</v>
       </c>
     </row>
